--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874F3728-A659-48E1-8EAF-902773E8D8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CB7B2F-C5E8-4043-8C4D-C57734DB5BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="64830" yWindow="2850" windowWidth="39795" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>год</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>Харьковская</t>
+  </si>
+  <si>
+    <t>Херсонская</t>
   </si>
 </sst>
 </file>
@@ -749,10 +752,16 @@
       <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1905</v>
+      </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="10">
+        <v>90646</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>

--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CB7B2F-C5E8-4043-8C4D-C57734DB5BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA0739E-5A80-4714-B7B1-C2047A029994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="64830" yWindow="2850" windowWidth="39795" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>год</t>
   </si>
@@ -105,7 +105,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +120,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -168,6 +174,9 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -765,27 +774,51 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1912</v>
+      </c>
+      <c r="C19" s="12">
+        <v>149228</v>
+      </c>
+      <c r="D19" s="12">
+        <v>71810</v>
+      </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1913</v>
+      </c>
+      <c r="C20" s="12">
+        <v>145478</v>
+      </c>
+      <c r="D20" s="12">
+        <v>86675</v>
+      </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C21" s="12">
+        <v>146669</v>
+      </c>
+      <c r="D21" s="12">
+        <v>81897</v>
+      </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>

--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA0739E-5A80-4714-B7B1-C2047A029994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF68A670-7476-4F03-B142-CF5C8F343C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="59640" yWindow="1680" windowWidth="26595" windowHeight="18210" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>год</t>
   </si>
@@ -105,7 +105,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,12 +120,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -172,11 +166,15 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,7 +505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.83984375" customWidth="1"/>
@@ -565,8 +563,8 @@
       <c r="B4" s="9">
         <v>1907</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12">
         <v>33399</v>
       </c>
       <c r="E4" s="10"/>
@@ -579,10 +577,10 @@
       <c r="B5" s="7">
         <v>1903</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="13">
         <v>64955</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="13">
         <v>46270</v>
       </c>
       <c r="E5" s="10"/>
@@ -595,10 +593,10 @@
       <c r="B6" s="7">
         <v>1904</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="13">
         <v>65478</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="13">
         <v>47869</v>
       </c>
       <c r="E6" s="10"/>
@@ -611,10 +609,10 @@
       <c r="B7" s="7">
         <v>1905</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="13">
         <v>65509</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="13">
         <v>45468</v>
       </c>
       <c r="E7" s="10"/>
@@ -627,10 +625,10 @@
       <c r="B8" s="7">
         <v>1906</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="13">
         <v>66434</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="13">
         <v>37381</v>
       </c>
       <c r="E8" s="10"/>
@@ -643,10 +641,10 @@
       <c r="B9" s="9">
         <v>1908</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="12">
         <v>62846</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>39384</v>
       </c>
       <c r="E9" s="10"/>
@@ -659,8 +657,8 @@
       <c r="B10" s="9">
         <v>1912</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12">
         <v>34926</v>
       </c>
       <c r="E10" s="10"/>
@@ -673,10 +671,10 @@
       <c r="B11" s="9">
         <v>1913</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="12">
         <v>206461</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>154406</v>
       </c>
       <c r="E11" s="10"/>
@@ -689,10 +687,10 @@
       <c r="B12" s="9">
         <v>1911</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="12">
         <v>139919</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="12">
         <v>94396</v>
       </c>
       <c r="E12" s="10"/>
@@ -705,8 +703,8 @@
       <c r="B13" s="9">
         <v>1882</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="10"/>
       <c r="F13" s="7"/>
     </row>
@@ -717,8 +715,8 @@
       <c r="B14" s="9">
         <v>1883</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="10"/>
       <c r="F14" s="7"/>
     </row>
@@ -729,8 +727,8 @@
       <c r="B15" s="9">
         <v>1901</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="10"/>
       <c r="F15" s="7"/>
     </row>
@@ -741,8 +739,8 @@
       <c r="B16" s="9">
         <v>1903</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="10"/>
       <c r="F16" s="7"/>
     </row>
@@ -753,8 +751,8 @@
       <c r="B17" s="9">
         <v>1882</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12">
         <v>64226</v>
       </c>
       <c r="E17" s="10"/>
@@ -767,66 +765,72 @@
       <c r="B18" s="7">
         <v>1905</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="10">
+      <c r="C18" s="14"/>
+      <c r="D18" s="12">
         <v>90646</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="7">
-        <v>1912</v>
-      </c>
-      <c r="C19" s="12">
-        <v>149228</v>
-      </c>
-      <c r="D19" s="12">
-        <v>71810</v>
-      </c>
+        <v>1909</v>
+      </c>
+      <c r="C19" s="11">
+        <v>139417</v>
+      </c>
+      <c r="D19" s="12"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C20" s="12">
-        <v>145478</v>
+        <v>149228</v>
       </c>
       <c r="D20" s="12">
-        <v>86675</v>
+        <v>71810</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C21" s="12">
-        <v>146669</v>
+        <v>145478</v>
       </c>
       <c r="D21" s="12">
-        <v>81897</v>
+        <v>86675</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="A22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C22" s="12">
+        <v>146669</v>
+      </c>
+      <c r="D22" s="12">
+        <v>81897</v>
+      </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
@@ -910,7 +914,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -918,7 +922,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -926,7 +930,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -934,15 +938,15 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="7"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -950,65 +954,61 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="2"/>
-    </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
       <c r="O49" s="3"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
@@ -1020,7 +1020,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
@@ -1032,80 +1032,82 @@
       <c r="O51" s="3"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
       <c r="O52" s="3"/>
       <c r="P52" s="2"/>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
       <c r="O53" s="3"/>
       <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-    </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
@@ -1115,27 +1117,27 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-    </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="G62" s="2"/>
@@ -1145,25 +1147,25 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-    </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
@@ -1172,7 +1174,8 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
@@ -1181,15 +1184,12 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
       <c r="O66" s="2"/>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
@@ -1210,11 +1210,20 @@
       <c r="O68" s="2"/>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
       <c r="O69" s="2"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
       <c r="O70" s="2"/>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1234,6 +1243,9 @@
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O77" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
